--- a/KatalonData/EmailTextToPay/Manage_EmailText_Demo.xlsx
+++ b/KatalonData/EmailTextToPay/Manage_EmailText_Demo.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="177">
   <si>
     <t>Result</t>
   </si>
@@ -419,6 +419,255 @@
   </si>
   <si>
     <t>Tue Jun 30 21:12:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:46:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:48:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:50:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:50:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:51:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:52:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:53:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:53:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:54:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:55:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:56:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:56:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:57:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:58:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:59:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:59:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:00:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:01:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:02:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:03:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:05:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:06:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:08:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:09:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:10:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:11:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:13:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:14:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:15:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:16:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:18:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:19:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:20:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:21:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:22:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:22:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:24:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:24:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:26:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:26:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 17:33:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 17:33:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 17:51:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 17:51:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 18:27:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:11:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:12:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:14:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:15:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:16:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:16:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:17:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:18:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:18:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:19:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:20:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:20:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:21:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:22:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:23:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:23:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:24:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:25:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:26:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:27:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:28:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:29:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:30:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:32:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:33:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:34:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:36:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:37:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:38:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:39:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:40:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:41:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:42:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:44:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:45:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:47:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:48:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:48:37 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -927,7 +1176,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="19" width="6.26953125" collapsed="true"/>
@@ -956,11 +1205,11 @@
       </c>
     </row>
     <row ht="13" r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>92</v>
+      <c r="A2" t="s" s="19">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="26">
+        <v>175</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>54</v>
@@ -973,11 +1222,11 @@
       </c>
     </row>
     <row ht="13" r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>93</v>
+      <c r="A3" t="s" s="19">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s" s="26">
+        <v>176</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>54</v>
@@ -1009,7 +1258,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB20ABE5-EB40-4301-BBE4-8B897354D04D}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="15.81640625" collapsed="true"/>
@@ -1039,11 +1288,11 @@
       </c>
     </row>
     <row customFormat="1" ht="75" r="2" s="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>67</v>
+      <c r="A2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>164</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>14</v>
@@ -1065,7 +1314,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03671AC8-56DE-457F-802A-D25D162F1818}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="15.1796875" collapsed="true"/>
@@ -1095,11 +1344,11 @@
       </c>
     </row>
     <row customFormat="1" ht="150" r="2" s="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>68</v>
+      <c r="A2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>141</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>15</v>
@@ -1121,7 +1370,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C8D7B23-96A3-4C14-84F1-69CBEB776D28}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="15.1796875" collapsed="true"/>
@@ -1151,11 +1400,11 @@
       </c>
     </row>
     <row customFormat="1" ht="150" r="2" s="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>69</v>
+      <c r="A2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>142</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>15</v>
@@ -1177,7 +1426,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EEFB455-878E-4283-8CDF-5280F5D2D976}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="15.1796875" collapsed="true"/>
@@ -1207,11 +1456,11 @@
       </c>
     </row>
     <row customFormat="1" ht="150" r="2" s="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>70</v>
+      <c r="A2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>140</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>15</v>
@@ -1233,7 +1482,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAC7F82F-C603-4F07-8548-EF17D188B148}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="1" width="8.7265625" collapsed="true"/>
@@ -1270,11 +1519,11 @@
       </c>
     </row>
     <row customHeight="1" ht="51.5" r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>71</v>
+      <c r="A2" t="s" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="1">
+        <v>151</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>32</v>
@@ -1291,11 +1540,11 @@
       <c r="E3" s="5"/>
     </row>
     <row ht="62.5" r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>72</v>
+      <c r="A4" t="s" s="1">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s" s="1">
+        <v>152</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>33</v>
@@ -1318,11 +1567,11 @@
       <c r="E5" s="5"/>
     </row>
     <row ht="75" r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>73</v>
+      <c r="A6" t="s" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s" s="1">
+        <v>153</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>28</v>
@@ -1341,11 +1590,11 @@
       </c>
     </row>
     <row ht="62.5" r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>74</v>
+      <c r="A7" t="s" s="1">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s" s="1">
+        <v>154</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>29</v>
@@ -1364,11 +1613,11 @@
       </c>
     </row>
     <row ht="75" r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>75</v>
+      <c r="A8" t="s" s="1">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s" s="1">
+        <v>155</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>30</v>
@@ -1387,11 +1636,11 @@
       </c>
     </row>
     <row ht="75" r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
-        <v>76</v>
+      <c r="A9" t="s" s="1">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s" s="1">
+        <v>156</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>31</v>
@@ -1410,11 +1659,11 @@
       </c>
     </row>
     <row ht="62.5" r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
-        <v>77</v>
+      <c r="A10" t="s" s="1">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s" s="1">
+        <v>157</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>43</v>
@@ -1433,11 +1682,11 @@
       </c>
     </row>
     <row ht="62.5" r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" t="s">
-        <v>78</v>
+      <c r="A11" t="s" s="1">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s" s="1">
+        <v>158</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>44</v>
@@ -1456,11 +1705,11 @@
       </c>
     </row>
     <row ht="62.5" r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" t="s">
-        <v>79</v>
+      <c r="A12" t="s" s="1">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s" s="1">
+        <v>159</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>45</v>
@@ -1485,7 +1734,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E26A7E4-F23A-4B0C-8BC6-AFD45C94E0CE}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="1" width="8.7265625" collapsed="true"/>
@@ -1522,11 +1771,11 @@
       </c>
     </row>
     <row ht="62.5" r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>80</v>
+      <c r="A2" t="s" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="1">
+        <v>143</v>
       </c>
       <c r="C2" s="18" t="s">
         <v>36</v>
@@ -1548,11 +1797,11 @@
       <c r="F3" s="5"/>
     </row>
     <row ht="62.5" r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>81</v>
+      <c r="A4" t="s" s="1">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s" s="1">
+        <v>144</v>
       </c>
       <c r="C4" s="18" t="s">
         <v>39</v>
@@ -1568,11 +1817,11 @@
       </c>
     </row>
     <row ht="62.5" r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>82</v>
+      <c r="A5" t="s" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s" s="1">
+        <v>145</v>
       </c>
       <c r="C5" s="18" t="s">
         <v>40</v>
@@ -1588,11 +1837,11 @@
       </c>
     </row>
     <row ht="62.5" r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>83</v>
+      <c r="A6" t="s" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s" s="1">
+        <v>146</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>41</v>
@@ -1611,11 +1860,11 @@
       <c r="C7" s="4"/>
     </row>
     <row customHeight="1" ht="55" r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>84</v>
+      <c r="A8" t="s" s="1">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s" s="1">
+        <v>147</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>21</v>
@@ -1634,11 +1883,11 @@
       </c>
     </row>
     <row customHeight="1" ht="55" r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
-        <v>85</v>
+      <c r="A9" t="s" s="1">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s" s="1">
+        <v>148</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>22</v>
@@ -1657,11 +1906,11 @@
       </c>
     </row>
     <row customHeight="1" ht="55" r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
-        <v>86</v>
+      <c r="A10" t="s" s="1">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s" s="1">
+        <v>149</v>
       </c>
       <c r="C10" s="18" t="s">
         <v>23</v>
@@ -1684,11 +1933,11 @@
       <c r="E11" s="5"/>
     </row>
     <row ht="50" r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" t="s">
-        <v>87</v>
+      <c r="A12" t="s" s="1">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s" s="1">
+        <v>150</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>38</v>
@@ -1712,7 +1961,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B68FE70-BD03-498B-B600-6B4B7C132BA1}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="16" width="7.26953125" collapsed="true"/>
@@ -1762,16 +2011,16 @@
       </c>
     </row>
     <row customFormat="1" ht="38" r="2" s="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>88</v>
+      <c r="A2" t="s" s="16">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="16">
+        <v>169</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="16">
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
@@ -1789,7 +2038,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2EABB53-51F5-4A90-B8E2-ADBC54583C91}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="16" width="7.26953125" collapsed="true"/>
@@ -1839,16 +2088,16 @@
       </c>
     </row>
     <row customFormat="1" ht="38" r="2" s="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>89</v>
+      <c r="A2" t="s" s="16">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="16">
+        <v>170</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="16">
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
@@ -1866,7 +2115,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DD67883-E46D-4766-8983-E96E92BD2427}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="16" width="7.26953125" collapsed="true"/>
@@ -1916,16 +2165,16 @@
       </c>
     </row>
     <row customFormat="1" ht="38" r="2" s="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>91</v>
+      <c r="A2" t="s" s="16">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="16">
+        <v>168</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="16">
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
@@ -1943,7 +2192,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="16" width="7.26953125" collapsed="true"/>
@@ -1993,16 +2242,16 @@
       </c>
     </row>
     <row customFormat="1" ht="25.5" r="2" s="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>59</v>
+      <c r="A2" t="s" s="16">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="16">
+        <v>166</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="16">
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
@@ -2020,7 +2269,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DBD4D3F-6789-4F69-A50C-D0C16059C617}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="6" width="7.26953125" collapsed="true"/>
@@ -2070,16 +2319,16 @@
       </c>
     </row>
     <row customFormat="1" ht="38" r="2" s="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>60</v>
+      <c r="A2" t="s" s="6">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="6">
+        <v>167</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="6">
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
@@ -2097,7 +2346,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D6A91F-B4A5-4069-ABF9-05ADE24D338D}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="6" width="7.26953125" collapsed="true"/>
@@ -2147,16 +2396,16 @@
       </c>
     </row>
     <row customFormat="1" ht="38" r="2" s="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
+      <c r="A2" t="s" s="6">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="6">
+        <v>165</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="6">
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
@@ -2174,7 +2423,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBD9BFD0-F930-4BCA-9C93-2C0B0F9DCF4B}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="16.0" collapsed="true"/>
@@ -2204,11 +2453,11 @@
       </c>
     </row>
     <row customFormat="1" customHeight="1" ht="78" r="2" s="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>62</v>
+      <c r="A2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>173</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>13</v>
@@ -2224,8 +2473,8 @@
       </c>
     </row>
     <row customFormat="1" customHeight="1" ht="19" r="3" s="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3"/>
-      <c r="B3"/>
+      <c r="A3" s="0"/>
+      <c r="B3" s="0"/>
       <c r="C3" s="7"/>
       <c r="D3" s="1"/>
       <c r="E3" s="5"/>
@@ -2243,7 +2492,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D613A990-B35A-40B9-8717-E014B2376EAA}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="16.0" collapsed="true"/>
@@ -2273,11 +2522,11 @@
       </c>
     </row>
     <row customFormat="1" customHeight="1" ht="78" r="2" s="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
+      <c r="A2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>174</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>51</v>
@@ -2293,8 +2542,8 @@
       </c>
     </row>
     <row customFormat="1" customHeight="1" ht="19" r="3" s="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3"/>
-      <c r="B3"/>
+      <c r="A3" s="0"/>
+      <c r="B3" s="0"/>
       <c r="C3" s="7"/>
       <c r="D3" s="1"/>
       <c r="E3" s="5"/>
@@ -2312,7 +2561,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3C48FAA-06E6-4269-9430-6E787AF33FF2}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="16.0" collapsed="true"/>
@@ -2342,11 +2591,11 @@
       </c>
     </row>
     <row customFormat="1" customHeight="1" ht="78" r="2" s="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>64</v>
+      <c r="A2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>172</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>52</v>
@@ -2377,7 +2626,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3B02ABF-6BE7-42F8-924B-66A45432828E}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="15.81640625" collapsed="true"/>
@@ -2407,11 +2656,11 @@
       </c>
     </row>
     <row customFormat="1" ht="75" r="2" s="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>65</v>
+      <c r="A2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>160</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>14</v>
@@ -2433,7 +2682,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80CBCA1D-16A9-43B0-BA4E-60CC8E0C88C7}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="15.81640625" collapsed="true"/>
@@ -2463,11 +2712,11 @@
       </c>
     </row>
     <row customFormat="1" ht="75" r="2" s="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>66</v>
+      <c r="A2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>161</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>14</v>
